--- a/paper_table1_summary.xlsx
+++ b/paper_table1_summary.xlsx
@@ -25,10 +25,10 @@
     <t xml:space="preserve">Avg. Execution Time (ms)</t>
   </si>
   <si>
-    <t xml:space="preserve">Rule-Based</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generative LLM (Gemini)</t>
+    <t xml:space="preserve">Rule-Based (Regex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generative LLM (Zero-Shot)</t>
   </si>
 </sst>
 </file>
@@ -296,13 +296,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="3">
-        <v>83.7</v>
+        <v>83.67</v>
       </c>
       <c r="C2" s="3">
-        <v>99.2</v>
+        <v>99.24</v>
       </c>
       <c r="D2" s="3">
-        <v>88.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="3">
@@ -310,13 +310,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="3">
-        <v>98.5</v>
+        <v>98.49</v>
       </c>
       <c r="C3" s="3">
-        <v>92.6</v>
+        <v>93.04</v>
       </c>
       <c r="D3" s="3">
-        <v>1320.0</v>
+        <v>1966.0</v>
       </c>
     </row>
   </sheetData>
